--- a/2026/BELTRAN 34/Febrero/Febrero BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Febrero/Febrero BELTRAN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELTRAN 34\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0C4995-F4BE-476A-BAD9-9AB944DF3335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA8B32C-5B90-40CE-9C27-0712643C110B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$97</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="132">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -334,12 +339,6 @@
   </si>
   <si>
     <t>SERVICIO DE LIMPIEZA</t>
-  </si>
-  <si>
-    <t>Celestino Soledad - Servicio de limpieza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorarios administracion </t>
   </si>
   <si>
     <t>Levy Lara</t>
@@ -366,33 +365,12 @@
     <t>Mes de DICIEMBRE</t>
   </si>
   <si>
-    <t>Cerrajera Citta - Copias de llaves</t>
-  </si>
-  <si>
-    <t>Transf 05/01</t>
-  </si>
-  <si>
-    <t>Debito 13/01</t>
-  </si>
-  <si>
-    <t>Transf 12/01</t>
-  </si>
-  <si>
-    <t>Ascensores Contessi - Reparacion según informe (ver informe y factura de reparacion de la apertura de bomberos)</t>
-  </si>
-  <si>
-    <t>Transf 30/01</t>
-  </si>
-  <si>
     <t>Ef.</t>
   </si>
   <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
-    <t>Matias Gonzalez</t>
-  </si>
-  <si>
     <t>Claudio Martuccio</t>
   </si>
   <si>
@@ -402,12 +380,6 @@
     <t>Bonificaciones banco santander</t>
   </si>
   <si>
-    <t>Dateas - solicitud de datos inicio ejecucion de datos</t>
-  </si>
-  <si>
-    <t>LA ADMINISTRACION CUENTA CON GASTOS A RECUPERAR (GASTOS QUE SE ABONAR EN EFECTIVO) QUE SUCEDERAN HASTA TRASPASAR LOS SEGUROS $67.154. LA SRA SOLEDAD TIENE A FAVOR DEL SERVICIO DE LIMPIEZA DEL MES DE FEBRERO $78.800</t>
-  </si>
-  <si>
     <t>VTO 13/03</t>
   </si>
   <si>
@@ -418,6 +390,45 @@
   </si>
   <si>
     <t>Ascensores Contessi - Provision y colocacion comando de techo en la cabina de ascensor CUOTA 2 DE 3 + Provision y colocacion de traba mecanica en las contactoras de subida y bajada de control</t>
+  </si>
+  <si>
+    <t>Debito 03/02</t>
+  </si>
+  <si>
+    <t>Transf 09/02</t>
+  </si>
+  <si>
+    <t>Transf 11/02</t>
+  </si>
+  <si>
+    <t>Transf 14/02</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Diciembre y Enero</t>
+  </si>
+  <si>
+    <t>Transf 18/02</t>
+  </si>
+  <si>
+    <t>Recarga anual de matafuegos - Valiente Sergio</t>
+  </si>
+  <si>
+    <t>Transf 23/02</t>
+  </si>
+  <si>
+    <t>Dra. Carina - Informe judicial</t>
+  </si>
+  <si>
+    <t>Transf 20/02</t>
+  </si>
+  <si>
+    <t>Celestino Soledad - Servicio de limpieza - No se abona por falta de caja</t>
+  </si>
+  <si>
+    <t>Matias Jose Medina Gonzalez</t>
+  </si>
+  <si>
+    <t>Ascensores Contessi -Adelanto arreglo según informe despues de apertura de bomberos 09/02</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1463,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1662,16 +1673,16 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="43" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1700,13 +1711,52 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1718,55 +1768,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1876,9 +1877,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1916,9 +1917,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1951,9 +1952,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1986,9 +2004,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2162,17 +2197,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L97"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2191,7 +2226,7 @@
       <c r="C2" s="97"/>
       <c r="D2" s="97"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="97" t="s">
         <v>65</v>
       </c>
@@ -2201,7 +2236,7 @@
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
       <c r="A4" s="162" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B4" s="162"/>
       <c r="C4" s="98"/>
@@ -2227,7 +2262,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="170" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2264,10 +2299,10 @@
       <c r="D17" s="165"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1"/>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
     <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
         <v>21</v>
@@ -2287,12 +2322,10 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="70" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="B23" s="70"/>
-      <c r="C23" s="144">
-        <v>184320</v>
-      </c>
+      <c r="C23" s="144"/>
       <c r="D23" s="70"/>
     </row>
     <row r="24" spans="1:7">
@@ -2302,7 +2335,7 @@
       <c r="B24" s="145"/>
       <c r="C24" s="95">
         <f>SUM(C23:C23)</f>
-        <v>184320</v>
+        <v>0</v>
       </c>
       <c r="D24" s="71"/>
     </row>
@@ -2349,7 +2382,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="72">
         <f>C24+C29</f>
-        <v>184320</v>
+        <v>0</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -2365,19 +2398,22 @@
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="128" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B32" s="147"/>
       <c r="C32" s="111">
-        <v>0</v>
-      </c>
-      <c r="D32" s="109"/>
+        <f>147400*2</f>
+        <v>294800</v>
+      </c>
+      <c r="D32" s="109" t="s">
+        <v>124</v>
+      </c>
       <c r="F32" s="33">
         <v>73700</v>
       </c>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="22" t="s">
         <v>29</v>
       </c>
@@ -2385,7 +2421,7 @@
       <c r="C33" s="27"/>
       <c r="D33" s="72">
         <f>SUM(C32:C32)</f>
-        <v>0</v>
+        <v>294800</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1">
@@ -2405,9 +2441,9 @@
         <v>23077</v>
       </c>
       <c r="D35" s="108" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="160">
+        <v>110</v>
+      </c>
+      <c r="F35" s="159">
         <f>C35*2</f>
         <v>46154</v>
       </c>
@@ -2421,10 +2457,10 @@
         <v>152897</v>
       </c>
       <c r="D36" s="108" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" thickBot="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1">
       <c r="A37" s="22" t="s">
         <v>1</v>
       </c>
@@ -2448,7 +2484,7 @@
         <v>59</v>
       </c>
       <c r="B39" s="70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C39" s="115"/>
       <c r="D39" s="108"/>
@@ -2459,7 +2495,7 @@
         <v>60</v>
       </c>
       <c r="B40" s="70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C40" s="116"/>
       <c r="D40" s="108"/>
@@ -2469,7 +2505,7 @@
         <v>61</v>
       </c>
       <c r="B41" s="70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C41" s="116"/>
       <c r="D41" s="108"/>
@@ -2479,7 +2515,7 @@
         <v>62</v>
       </c>
       <c r="B42" s="70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C42" s="116"/>
       <c r="D42" s="107"/>
@@ -2508,11 +2544,11 @@
         <v>98</v>
       </c>
       <c r="B45" s="70"/>
-      <c r="C45" s="193">
+      <c r="C45" s="116">
         <v>104732.54</v>
       </c>
       <c r="D45" s="106" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1">
@@ -2520,14 +2556,14 @@
         <v>99</v>
       </c>
       <c r="B46" s="70"/>
-      <c r="C46" s="193">
+      <c r="C46" s="116">
         <v>354392.42</v>
       </c>
       <c r="D46" s="106" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
       <c r="A47" s="22" t="s">
         <v>3</v>
       </c>
@@ -2538,7 +2574,7 @@
         <v>459124.95999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15" thickBot="1">
+    <row r="48" spans="1:6" ht="15.75" thickBot="1">
       <c r="A48" s="21" t="s">
         <v>31</v>
       </c>
@@ -2548,389 +2584,374 @@
     </row>
     <row r="49" spans="1:6" ht="50.25" customHeight="1">
       <c r="A49" s="163" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B49" s="164"/>
-      <c r="C49" s="193">
+      <c r="C49" s="116">
         <v>370000</v>
       </c>
       <c r="D49" s="103" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="50.25" customHeight="1">
       <c r="A50" s="163" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B50" s="164"/>
-      <c r="C50" s="193">
+      <c r="C50" s="116">
+        <v>400000</v>
+      </c>
+      <c r="D50" s="103" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="50.25" customHeight="1">
+      <c r="A51" s="163" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="164"/>
+      <c r="C51" s="116">
         <v>105000</v>
       </c>
-      <c r="D50" s="103" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1">
-      <c r="A51" s="171" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="172"/>
-      <c r="C51" s="116">
-        <v>10000</v>
-      </c>
       <c r="D51" s="103" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1">
-      <c r="A52" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="50.25" customHeight="1">
+      <c r="A52" s="163" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="164"/>
+      <c r="C52" s="116">
+        <v>110000</v>
+      </c>
+      <c r="D52" s="103" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A53" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="80">
-        <f>SUM(C49:C51)</f>
-        <v>485000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1">
-      <c r="A53" s="21" t="s">
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="80">
+        <f>SUM(C49:C52)</f>
+        <v>985000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A54" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B53" s="149"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="77"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" s="70"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="81"/>
+      <c r="B54" s="149"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="77"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="70" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="B55" s="70"/>
-      <c r="C55" s="116">
-        <v>32988.99</v>
-      </c>
-      <c r="D55" s="79"/>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
-      <c r="A56" s="150" t="s">
+      <c r="C55" s="118"/>
+      <c r="D55" s="81"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="70"/>
+      <c r="C56" s="116">
+        <v>26007.360000000001</v>
+      </c>
+      <c r="D56" s="79"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A57" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="B56" s="150"/>
-      <c r="C56" s="82"/>
-      <c r="D56" s="74">
-        <f>SUM(C54:C55)</f>
-        <v>32988.99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1">
-      <c r="A57" s="70"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="83"/>
-    </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A58" s="167" t="s">
-        <v>119</v>
-      </c>
-      <c r="B58" s="168"/>
-      <c r="C58" s="169"/>
-      <c r="D58" s="84"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1">
-      <c r="A59" s="151"/>
-      <c r="B59" s="85"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="86"/>
-      <c r="E59" s="35"/>
-    </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1">
-      <c r="A60" s="152" t="s">
+      <c r="B57" s="150"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="74">
+        <f>SUM(C55:C56)</f>
+        <v>26007.360000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A58" s="70"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="83"/>
+    </row>
+    <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A59" s="167" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="168"/>
+      <c r="C59" s="169"/>
+      <c r="D59" s="84"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A60" s="151"/>
+      <c r="B60" s="85"/>
+      <c r="C60" s="85"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="35"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A61" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="153"/>
-      <c r="C60" s="87"/>
-      <c r="D60" s="88">
-        <f>(SUM(D25:D58))</f>
-        <v>1337407.95</v>
-      </c>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="85"/>
-      <c r="B61" s="85"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="85"/>
-      <c r="F61" s="102"/>
-    </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1">
+      <c r="B61" s="153"/>
+      <c r="C61" s="87"/>
+      <c r="D61" s="88">
+        <f>(SUM(D25:D59))</f>
+        <v>1940906.32</v>
+      </c>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="85"/>
       <c r="B62" s="85"/>
       <c r="C62" s="85"/>
       <c r="D62" s="85"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="154" t="s">
+      <c r="F62" s="102"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A63" s="85"/>
+      <c r="B63" s="85"/>
+      <c r="C63" s="85"/>
+      <c r="D63" s="85"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="B63" s="155"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="90"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="163" t="s">
-        <v>124</v>
-      </c>
-      <c r="B64" s="164"/>
-      <c r="C64" s="78">
-        <v>11000</v>
-      </c>
-      <c r="D64" s="103" t="s">
-        <v>118</v>
-      </c>
+      <c r="B64" s="155"/>
+      <c r="C64" s="89"/>
+      <c r="D64" s="90"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="163"/>
-      <c r="B65" s="164"/>
-      <c r="C65" s="78"/>
-      <c r="D65" s="76"/>
+      <c r="A65" s="160" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="161"/>
+      <c r="C65" s="116">
+        <v>21000</v>
+      </c>
+      <c r="D65" s="103" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="93"/>
-      <c r="B66" s="94"/>
+      <c r="A66" s="163"/>
+      <c r="B66" s="164"/>
       <c r="C66" s="78"/>
       <c r="D66" s="76"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="38"/>
-      <c r="B67" s="37"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42">
-        <f>SUM(C64:C66)</f>
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15" customHeight="1"/>
-    <row r="69" spans="1:4" hidden="1"/>
-    <row r="70" spans="1:4">
-      <c r="A70" s="17" t="s">
+      <c r="A67" s="93"/>
+      <c r="B67" s="94"/>
+      <c r="C67" s="78"/>
+      <c r="D67" s="76"/>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="38"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42">
+        <f>SUM(C65:C67)</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15" customHeight="1"/>
+    <row r="70" spans="1:4" hidden="1"/>
+    <row r="71" spans="1:4">
+      <c r="A71" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1"/>
-    <row r="72" spans="1:4" ht="15" thickBot="1">
-      <c r="A72" s="2" t="s">
+      <c r="B71" s="17"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1"/>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A73" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="48">
-        <f>D67+D70</f>
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1"/>
-    <row r="74" spans="1:4" ht="15" thickBot="1">
-      <c r="A74" s="68" t="s">
+      <c r="B73" s="8"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="48">
+        <f>D68+D71</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1"/>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A75" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B74" s="69">
-        <f>D60</f>
-        <v>1337407.95</v>
-      </c>
-      <c r="C74" s="35"/>
-    </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1">
-      <c r="A75" s="68" t="s">
+      <c r="B75" s="69">
+        <f>D61</f>
+        <v>1940906.32</v>
+      </c>
+      <c r="C75" s="35"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B75" s="69">
-        <f>D60-D58</f>
-        <v>1337407.95</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1">
-      <c r="A76" s="68" t="s">
+      <c r="B76" s="69">
+        <f>D61-D59</f>
+        <v>1940906.32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A77" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="B76" s="69">
-        <f>D72-D70</f>
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1">
-      <c r="A77" s="68" t="s">
+      <c r="B77" s="69">
+        <f>D73-D71</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A78" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="B77" s="69">
-        <f>D72</f>
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="173" t="s">
-        <v>125</v>
-      </c>
-      <c r="B80" s="173"/>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="173"/>
-      <c r="B81" s="173"/>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="173"/>
-      <c r="B82" s="173"/>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="173"/>
-      <c r="B83" s="173"/>
-    </row>
-    <row r="87" spans="1:3" ht="15" thickBot="1">
-      <c r="A87" s="13" t="s">
+      <c r="B78" s="69">
+        <f>D73</f>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A82" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B87" s="127"/>
-    </row>
-    <row r="88" spans="1:3" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A88" s="20" t="s">
+      <c r="B82" s="127"/>
+    </row>
+    <row r="83" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A83" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B88" s="159">
-        <v>159602.50000000023</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A89" s="14" t="s">
+      <c r="B83" s="158">
+        <v>487362.16999999993</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A84" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B89" s="32">
+      <c r="B84" s="32">
         <f>PRORRATEO!H24</f>
-        <v>2022091.92</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A90" s="14" t="s">
+        <v>1320859.99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A85" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B90" s="79">
-        <f>B102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="13.95" customHeight="1">
-      <c r="A91" s="15" t="s">
+      <c r="B85" s="79">
+        <f>B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="13.9" customHeight="1">
+      <c r="A86" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B91" s="105"/>
-    </row>
-    <row r="92" spans="1:3" ht="65.25" customHeight="1">
-      <c r="A92" s="161" t="s">
-        <v>116</v>
-      </c>
-      <c r="B92" s="157">
-        <v>-480000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="13.95" customHeight="1">
-      <c r="A93" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B93" s="79">
-        <f>141260.13+61769.13</f>
-        <v>203029.26</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="31" t="s">
+      <c r="B86" s="105"/>
+    </row>
+    <row r="87" spans="1:4" ht="13.9" customHeight="1">
+      <c r="A87" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B87" s="79">
+        <f>52366.67+144594.47</f>
+        <v>196961.14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B94" s="105">
-        <f>-B75</f>
-        <v>-1337407.95</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="15" t="s">
+      <c r="B88" s="105">
+        <f>-B76</f>
+        <v>-1940906.32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B95" s="79">
-        <f>-(B76)</f>
-        <v>-11000</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="19" t="s">
+      <c r="B89" s="105">
+        <f>-(B77)</f>
+        <v>-21000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B96" s="129">
-        <f>SUM(B88:B95)</f>
-        <v>556315.73</v>
-      </c>
-      <c r="C96" s="158"/>
-    </row>
-    <row r="97" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B97" s="33"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="158"/>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" s="166" t="s">
+      <c r="B90" s="129">
+        <f>SUM(B83:B89)</f>
+        <v>43276.979999999749</v>
+      </c>
+      <c r="C90" s="157"/>
+    </row>
+    <row r="91" spans="1:4" ht="34.5" customHeight="1">
+      <c r="B91" s="33"/>
+      <c r="C91" s="35"/>
+      <c r="D91" s="157"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="166" t="s">
         <v>46</v>
       </c>
-      <c r="B98" s="166"/>
-    </row>
-    <row r="99" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A99" s="166"/>
-      <c r="B99" s="166"/>
-    </row>
-    <row r="100" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A100" s="91"/>
-      <c r="B100" s="26"/>
-    </row>
-    <row r="101" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A101" s="91"/>
-      <c r="B101" s="26"/>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" s="36" t="s">
+      <c r="B92" s="166"/>
+    </row>
+    <row r="93" spans="1:4" ht="27.75" customHeight="1">
+      <c r="A93" s="166"/>
+      <c r="B93" s="166"/>
+    </row>
+    <row r="94" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A94" s="91"/>
+      <c r="B94" s="26"/>
+    </row>
+    <row r="95" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A95" s="91"/>
+      <c r="B95" s="26"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B102" s="92">
-        <f>SUM(B100:B101)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="L103" s="6"/>
+      <c r="B96" s="92">
+        <f>SUM(B94:B95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="12:12">
+      <c r="L97" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A98:B99"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A92:B93"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A80:B83"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2941,48 +2962,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="130"/>
-      <c r="B1" s="178" t="str">
+      <c r="B1" s="171" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
       <c r="L1" s="131"/>
       <c r="M1" s="131"/>
       <c r="N1" s="131"/>
@@ -2991,24 +3012,23 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="133"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="179"/>
-      <c r="K2" s="179"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
       <c r="L2" s="134"/>
       <c r="M2" s="134" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="5"/>
       <c r="O2" s="142">
-        <f>R2</f>
-        <v>1406361.51</v>
+        <v>1700000</v>
       </c>
       <c r="P2" s="135"/>
       <c r="Q2" s="12"/>
@@ -3018,118 +3038,118 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="136"/>
-      <c r="B3" s="180"/>
-      <c r="C3" s="180"/>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="180"/>
-      <c r="H3" s="180"/>
-      <c r="I3" s="180"/>
-      <c r="J3" s="180"/>
-      <c r="K3" s="180"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
       <c r="L3" s="137"/>
       <c r="M3" s="137" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="138"/>
       <c r="O3" s="143">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="P3" s="139"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="191"/>
-      <c r="L4" s="191"/>
-      <c r="M4" s="191"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="191"/>
-      <c r="P4" s="192"/>
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
+      <c r="H4" s="185"/>
+      <c r="I4" s="185"/>
+      <c r="J4" s="185"/>
+      <c r="K4" s="185"/>
+      <c r="L4" s="185"/>
+      <c r="M4" s="185"/>
+      <c r="N4" s="185"/>
+      <c r="O4" s="185"/>
+      <c r="P4" s="186"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="177" t="s">
+      <c r="D5" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="177" t="s">
+      <c r="E5" s="176" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="177" t="s">
+      <c r="F5" s="176" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="177" t="s">
+      <c r="G5" s="176" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="177" t="s">
+      <c r="H5" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="177" t="s">
+      <c r="I5" s="176" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="186" t="s">
+      <c r="J5" s="180" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="184" t="s">
+      <c r="K5" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="184" t="s">
+      <c r="L5" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="184" t="s">
+      <c r="M5" s="178" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="188" t="s">
+      <c r="N5" s="182" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="181" t="s">
+      <c r="P5" s="174" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="35"/>
       <c r="T5" s="33"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="175"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="185"/>
-      <c r="N6" s="189"/>
+      <c r="A6" s="188"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="181"/>
+      <c r="K6" s="179"/>
+      <c r="L6" s="178"/>
+      <c r="M6" s="179"/>
+      <c r="N6" s="183"/>
       <c r="O6" s="43" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P6" s="181"/>
+      <c r="P6" s="174"/>
       <c r="S6" s="33">
         <v>65160</v>
       </c>
@@ -3159,36 +3179,36 @@
         <v>10.86</v>
       </c>
       <c r="G7" s="50">
-        <v>2997197.01</v>
+        <v>3241038.01</v>
       </c>
       <c r="H7" s="51"/>
       <c r="I7" s="52"/>
       <c r="J7" s="53">
         <f>G7-H7</f>
-        <v>2997197.01</v>
+        <v>3241038.01</v>
       </c>
       <c r="K7" s="53">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>89915.910299999989</v>
+        <v>97231.140299999985</v>
       </c>
       <c r="L7" s="54">
         <f>O$3*F7%</f>
-        <v>1194.5999999999999</v>
+        <v>2280.6</v>
       </c>
       <c r="M7" s="54">
         <f>O$2*F7%</f>
-        <v>152730.859986</v>
+        <v>184619.99999999997</v>
       </c>
       <c r="N7" s="55">
         <v>0</v>
       </c>
       <c r="O7" s="56">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>3241038.01</v>
+        <v>3525170.01</v>
       </c>
       <c r="P7" s="57">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>3338269.01</v>
+        <v>3630925.01</v>
       </c>
       <c r="Q7" s="35">
         <v>0.01</v>
@@ -3222,11 +3242,11 @@
         <v>11.16</v>
       </c>
       <c r="G8" s="50">
-        <v>207261.02</v>
+        <v>162923.01999999999</v>
       </c>
       <c r="H8" s="51">
-        <f>217829.14-H18</f>
-        <v>207261.02000000002</v>
+        <f>171244.14-H18</f>
+        <v>162923.02000000002</v>
       </c>
       <c r="I8" s="52"/>
       <c r="J8" s="53">
@@ -3239,22 +3259,22 @@
       </c>
       <c r="L8" s="54">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
-        <v>1227.6000000000001</v>
+        <v>2343.6</v>
       </c>
       <c r="M8" s="54">
         <f t="shared" ref="M8:M23" si="5">O$2*F8%</f>
-        <v>156949.94451600002</v>
+        <v>189720</v>
       </c>
       <c r="N8" s="55">
         <v>0</v>
       </c>
       <c r="O8" s="56">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>158178.01999999999</v>
+        <v>192064.02</v>
       </c>
       <c r="P8" s="57">
         <f t="shared" si="0"/>
-        <v>162923.01999999999</v>
+        <v>197826.02</v>
       </c>
       <c r="Q8" s="35">
         <f>Q7+0.01</f>
@@ -3286,44 +3306,45 @@
         <v>88</v>
       </c>
       <c r="E9" s="104" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F9" s="121">
         <v>6.95</v>
       </c>
       <c r="G9" s="51">
-        <v>147207.03</v>
+        <v>150722.03</v>
       </c>
       <c r="H9" s="51">
-        <v>100775</v>
+        <f>G9</f>
+        <v>150722.03</v>
       </c>
       <c r="I9" s="52"/>
       <c r="J9" s="122">
         <f t="shared" si="2"/>
-        <v>46432.03</v>
+        <v>0</v>
       </c>
       <c r="K9" s="53">
         <f t="shared" si="3"/>
-        <v>1392.9608999999998</v>
+        <v>0</v>
       </c>
       <c r="L9" s="123">
         <f t="shared" si="4"/>
-        <v>764.50000000000011</v>
+        <v>1459.5000000000002</v>
       </c>
       <c r="M9" s="123">
         <f t="shared" si="5"/>
-        <v>97742.124945000003</v>
+        <v>118150.00000000001</v>
       </c>
       <c r="N9" s="124">
         <v>0</v>
       </c>
       <c r="O9" s="125">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>146332.03</v>
+        <v>119610.03</v>
       </c>
       <c r="P9" s="126">
         <f t="shared" si="0"/>
-        <v>150722.03</v>
+        <v>123198.03</v>
       </c>
       <c r="Q9" s="35">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
@@ -3354,45 +3375,45 @@
         <v>89</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F10" s="49">
         <v>7.37</v>
       </c>
       <c r="G10" s="50">
-        <v>288278.03999999998</v>
+        <v>104179.04</v>
       </c>
       <c r="H10" s="51">
-        <f>297919-H20</f>
-        <v>288558.86</v>
+        <f>110962-H20</f>
+        <v>103591.86</v>
       </c>
       <c r="I10" s="52"/>
       <c r="J10" s="53">
         <f t="shared" si="2"/>
-        <v>-280.82000000000698</v>
+        <v>587.17999999999302</v>
       </c>
       <c r="K10" s="53">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17.615399999999791</v>
       </c>
       <c r="L10" s="54">
         <f t="shared" si="4"/>
-        <v>810.7</v>
+        <v>1547.7</v>
       </c>
       <c r="M10" s="54">
         <f t="shared" si="5"/>
-        <v>103648.843287</v>
+        <v>125290</v>
       </c>
       <c r="N10" s="55">
         <v>0</v>
       </c>
       <c r="O10" s="56">
         <f t="shared" si="6"/>
-        <v>104179.04</v>
+        <v>127442.04</v>
       </c>
       <c r="P10" s="57">
         <f t="shared" si="0"/>
-        <v>107304.04</v>
+        <v>131265.03999999998</v>
       </c>
       <c r="Q10" s="35">
         <f t="shared" si="7"/>
@@ -3423,45 +3444,45 @@
         <v>90</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F11" s="49">
         <v>10.68</v>
       </c>
       <c r="G11" s="50">
-        <v>192240.05</v>
+        <v>151374.04999999999</v>
       </c>
       <c r="H11" s="51">
-        <f>G11</f>
-        <v>192240.05</v>
+        <f>1175+150199</f>
+        <v>151374</v>
       </c>
       <c r="I11" s="52"/>
       <c r="J11" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.9999999988358468E-2</v>
       </c>
       <c r="K11" s="53">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.499999999650754E-3</v>
       </c>
       <c r="L11" s="54">
         <f t="shared" si="4"/>
-        <v>1174.8</v>
+        <v>2242.7999999999997</v>
       </c>
       <c r="M11" s="54">
         <f t="shared" si="5"/>
-        <v>150199.40926799999</v>
+        <v>181560</v>
       </c>
       <c r="N11" s="55">
         <v>0</v>
       </c>
       <c r="O11" s="56">
         <f t="shared" si="6"/>
-        <v>151374.04999999999</v>
+        <v>183803.05</v>
       </c>
       <c r="P11" s="57">
         <f t="shared" si="0"/>
-        <v>155915.04999999999</v>
+        <v>189317.05</v>
       </c>
       <c r="Q11" s="35">
         <f t="shared" si="7"/>
@@ -3492,45 +3513,45 @@
         <v>91</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F12" s="49">
         <v>6.95</v>
       </c>
       <c r="G12" s="50">
-        <v>125100.06</v>
+        <v>578507.06000000006</v>
       </c>
       <c r="H12" s="51">
-        <f>136080-H22</f>
-        <v>125099.84</v>
+        <f>832+98510</f>
+        <v>99342</v>
       </c>
       <c r="I12" s="52"/>
       <c r="J12" s="53">
         <f t="shared" si="2"/>
-        <v>0.22000000000116415</v>
+        <v>479165.06000000006</v>
       </c>
       <c r="K12" s="53">
         <f t="shared" si="3"/>
-        <v>6.6000000000349243E-3</v>
+        <v>14374.951800000001</v>
       </c>
       <c r="L12" s="54">
         <f t="shared" si="4"/>
-        <v>764.50000000000011</v>
+        <v>1459.5000000000002</v>
       </c>
       <c r="M12" s="54">
         <f t="shared" si="5"/>
-        <v>97742.124945000003</v>
+        <v>118150.00000000001</v>
       </c>
       <c r="N12" s="156">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="O12" s="56">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>578507.06000000006</v>
+        <v>613150.06000000006</v>
       </c>
       <c r="P12" s="57">
         <f t="shared" si="0"/>
-        <v>595862.06000000006</v>
+        <v>631545.06000000006</v>
       </c>
       <c r="Q12" s="35">
         <f t="shared" si="7"/>
@@ -3561,22 +3582,21 @@
         <v>92</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F13" s="49">
         <v>6.89</v>
       </c>
       <c r="G13" s="50">
-        <v>124020.07</v>
+        <v>97656.07</v>
       </c>
       <c r="H13" s="51">
-        <f t="shared" ref="H13:H18" si="8">G13</f>
-        <v>124020.07</v>
+        <v>100586.07</v>
       </c>
       <c r="I13" s="52"/>
       <c r="J13" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2930</v>
       </c>
       <c r="K13" s="53">
         <f t="shared" si="3"/>
@@ -3584,22 +3604,22 @@
       </c>
       <c r="L13" s="54">
         <f t="shared" si="4"/>
-        <v>757.9</v>
+        <v>1446.9</v>
       </c>
       <c r="M13" s="54">
         <f t="shared" si="5"/>
-        <v>96898.30803900001</v>
+        <v>117130</v>
       </c>
       <c r="N13" s="55">
         <v>0</v>
       </c>
       <c r="O13" s="56">
         <f t="shared" si="6"/>
-        <v>97656.07</v>
+        <v>115647.07</v>
       </c>
       <c r="P13" s="57">
         <f t="shared" si="0"/>
-        <v>100586.07</v>
+        <v>119116.07</v>
       </c>
       <c r="Q13" s="35">
         <f t="shared" si="7"/>
@@ -3631,17 +3651,17 @@
         <v>92</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F14" s="49">
         <v>10.68</v>
       </c>
       <c r="G14" s="50">
-        <v>192240.08</v>
+        <v>151374.07999999999</v>
       </c>
       <c r="H14" s="51">
-        <f t="shared" si="8"/>
-        <v>192240.08</v>
+        <f t="shared" ref="H13:H18" si="8">G14</f>
+        <v>151374.07999999999</v>
       </c>
       <c r="I14" s="52"/>
       <c r="J14" s="53">
@@ -3654,22 +3674,22 @@
       </c>
       <c r="L14" s="54">
         <f t="shared" si="4"/>
-        <v>1174.8</v>
+        <v>2242.7999999999997</v>
       </c>
       <c r="M14" s="54">
         <f t="shared" si="5"/>
-        <v>150199.40926799999</v>
+        <v>181560</v>
       </c>
       <c r="N14" s="55">
         <v>0</v>
       </c>
       <c r="O14" s="56">
         <f t="shared" si="6"/>
-        <v>151374.07999999999</v>
+        <v>183803.08</v>
       </c>
       <c r="P14" s="57">
         <f t="shared" si="0"/>
-        <v>155915.07999999999</v>
+        <v>189317.08</v>
       </c>
       <c r="Q14" s="35">
         <f t="shared" si="7"/>
@@ -3704,16 +3724,16 @@
         <v>6.95</v>
       </c>
       <c r="G15" s="51">
-        <v>142301.09</v>
+        <v>98507.09</v>
       </c>
       <c r="H15" s="141">
-        <f t="shared" si="8"/>
-        <v>142301.09</v>
+        <f>98507.09+765.09</f>
+        <v>99272.18</v>
       </c>
       <c r="I15" s="52"/>
       <c r="J15" s="122">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-765.08999999999651</v>
       </c>
       <c r="K15" s="122">
         <f t="shared" si="3"/>
@@ -3721,22 +3741,22 @@
       </c>
       <c r="L15" s="123">
         <f t="shared" si="4"/>
-        <v>764.50000000000011</v>
+        <v>1459.5000000000002</v>
       </c>
       <c r="M15" s="123">
         <f t="shared" si="5"/>
-        <v>97742.124945000003</v>
+        <v>118150.00000000001</v>
       </c>
       <c r="N15" s="124">
         <v>0</v>
       </c>
       <c r="O15" s="125">
         <f t="shared" si="6"/>
-        <v>98507.09</v>
+        <v>118844.09</v>
       </c>
       <c r="P15" s="126">
         <f t="shared" si="0"/>
-        <v>101462.09</v>
+        <v>122409.09</v>
       </c>
       <c r="Q15" s="35">
         <f t="shared" si="7"/>
@@ -3767,17 +3787,17 @@
         <v>94</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F16" s="49">
         <v>6.89</v>
       </c>
       <c r="G16" s="50">
-        <v>124020.1</v>
+        <v>97656.1</v>
       </c>
       <c r="H16" s="51">
         <f t="shared" si="8"/>
-        <v>124020.1</v>
+        <v>97656.1</v>
       </c>
       <c r="I16" s="52"/>
       <c r="J16" s="53">
@@ -3790,22 +3810,22 @@
       </c>
       <c r="L16" s="54">
         <f t="shared" si="4"/>
-        <v>757.9</v>
+        <v>1446.9</v>
       </c>
       <c r="M16" s="54">
         <f t="shared" si="5"/>
-        <v>96898.30803900001</v>
+        <v>117130</v>
       </c>
       <c r="N16" s="55">
         <v>0</v>
       </c>
       <c r="O16" s="56">
         <f t="shared" si="6"/>
-        <v>97656.1</v>
+        <v>118577.1</v>
       </c>
       <c r="P16" s="57">
         <f t="shared" si="0"/>
-        <v>100586.1</v>
+        <v>122134.1</v>
       </c>
       <c r="Q16" s="35">
         <f t="shared" si="7"/>
@@ -3840,16 +3860,15 @@
         <v>11.88</v>
       </c>
       <c r="G17" s="50">
-        <v>464686.11</v>
+        <v>168383.11</v>
       </c>
       <c r="H17" s="51">
-        <f t="shared" si="8"/>
-        <v>464686.11</v>
+        <v>173434.11</v>
       </c>
       <c r="I17" s="52"/>
       <c r="J17" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5051</v>
       </c>
       <c r="K17" s="53">
         <f t="shared" si="3"/>
@@ -3857,22 +3876,22 @@
       </c>
       <c r="L17" s="54">
         <f t="shared" si="4"/>
-        <v>1306.8</v>
+        <v>2494.8000000000002</v>
       </c>
       <c r="M17" s="54">
         <f t="shared" si="5"/>
-        <v>167075.74738800002</v>
+        <v>201960</v>
       </c>
       <c r="N17" s="55">
         <v>0</v>
       </c>
       <c r="O17" s="56">
         <f t="shared" si="6"/>
-        <v>168383.11</v>
+        <v>199404.11</v>
       </c>
       <c r="P17" s="57">
         <f t="shared" si="0"/>
-        <v>173434.11</v>
+        <v>205386.11</v>
       </c>
       <c r="Q17" s="35">
         <f t="shared" si="7"/>
@@ -3907,11 +3926,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G18" s="50">
-        <v>10568.12</v>
+        <v>8321.119999999999</v>
       </c>
       <c r="H18" s="51">
         <f t="shared" si="8"/>
-        <v>10568.12</v>
+        <v>8321.119999999999</v>
       </c>
       <c r="I18" s="52"/>
       <c r="J18" s="53">
@@ -3924,22 +3943,22 @@
       </c>
       <c r="L18" s="54">
         <f t="shared" si="4"/>
-        <v>62.699999999999996</v>
+        <v>119.69999999999999</v>
       </c>
       <c r="M18" s="54">
         <f t="shared" si="5"/>
-        <v>8016.2606069999993</v>
+        <v>9689.9999999999982</v>
       </c>
       <c r="N18" s="55">
         <v>0</v>
       </c>
       <c r="O18" s="56">
         <f t="shared" si="6"/>
-        <v>8079.12</v>
+        <v>9810.1200000000008</v>
       </c>
       <c r="P18" s="57">
         <f t="shared" si="0"/>
-        <v>8321.119999999999</v>
+        <v>10104.120000000001</v>
       </c>
       <c r="Q18" s="35">
         <f t="shared" si="7"/>
@@ -3974,15 +3993,15 @@
         <v>0.52</v>
       </c>
       <c r="G19" s="50">
-        <v>9360.1299999999992</v>
+        <v>7089.13</v>
       </c>
       <c r="H19" s="51">
-        <v>9641.1299999999992</v>
+        <v>7302.13</v>
       </c>
       <c r="I19" s="52"/>
       <c r="J19" s="53">
         <f t="shared" si="2"/>
-        <v>-281</v>
+        <v>-213</v>
       </c>
       <c r="K19" s="53">
         <f t="shared" si="3"/>
@@ -3990,22 +4009,22 @@
       </c>
       <c r="L19" s="54">
         <f t="shared" si="4"/>
-        <v>57.199999999999996</v>
+        <v>109.19999999999999</v>
       </c>
       <c r="M19" s="54">
         <f t="shared" si="5"/>
-        <v>7313.0798519999998</v>
+        <v>8840</v>
       </c>
       <c r="N19" s="55">
         <v>0</v>
       </c>
       <c r="O19" s="56">
         <f t="shared" si="6"/>
-        <v>7089.13</v>
+        <v>8736.1299999999992</v>
       </c>
       <c r="P19" s="57">
         <f t="shared" si="0"/>
-        <v>7302.13</v>
+        <v>8998.1299999999992</v>
       </c>
       <c r="Q19" s="35">
         <f t="shared" si="7"/>
@@ -4036,17 +4055,17 @@
         <v>96</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F20" s="49">
         <v>0.52</v>
       </c>
       <c r="G20" s="50">
-        <v>9360.14</v>
+        <v>7370.14</v>
       </c>
       <c r="H20" s="51">
         <f>G20</f>
-        <v>9360.14</v>
+        <v>7370.14</v>
       </c>
       <c r="I20" s="52"/>
       <c r="J20" s="53">
@@ -4059,22 +4078,22 @@
       </c>
       <c r="L20" s="54">
         <f t="shared" si="4"/>
-        <v>57.199999999999996</v>
+        <v>109.19999999999999</v>
       </c>
       <c r="M20" s="54">
         <f t="shared" si="5"/>
-        <v>7313.0798519999998</v>
+        <v>8840</v>
       </c>
       <c r="N20" s="55">
         <v>0</v>
       </c>
       <c r="O20" s="56">
         <f t="shared" si="6"/>
-        <v>7370.14</v>
+        <v>8949.14</v>
       </c>
       <c r="P20" s="57">
         <f t="shared" si="0"/>
-        <v>7591.14</v>
+        <v>9217.14</v>
       </c>
       <c r="Q20" s="35">
         <f t="shared" si="7"/>
@@ -4109,16 +4128,15 @@
         <v>0.52</v>
       </c>
       <c r="G21" s="50">
-        <v>20340.150000000001</v>
+        <v>7370.15</v>
       </c>
       <c r="H21" s="51">
-        <f>G21</f>
-        <v>20340.150000000001</v>
+        <v>7591.15</v>
       </c>
       <c r="I21" s="52"/>
       <c r="J21" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-221</v>
       </c>
       <c r="K21" s="53">
         <f t="shared" si="3"/>
@@ -4126,22 +4144,22 @@
       </c>
       <c r="L21" s="54">
         <f t="shared" si="4"/>
-        <v>57.199999999999996</v>
+        <v>109.19999999999999</v>
       </c>
       <c r="M21" s="54">
         <f t="shared" si="5"/>
-        <v>7313.0798519999998</v>
+        <v>8840</v>
       </c>
       <c r="N21" s="55">
         <v>0</v>
       </c>
       <c r="O21" s="56">
         <f t="shared" si="6"/>
-        <v>7370.15</v>
+        <v>8728.15</v>
       </c>
       <c r="P21" s="57">
         <f t="shared" si="0"/>
-        <v>7591.15</v>
+        <v>8990.15</v>
       </c>
       <c r="Q21" s="35">
         <f t="shared" si="7"/>
@@ -4176,39 +4194,36 @@
         <v>0.61</v>
       </c>
       <c r="G22" s="50">
-        <v>10980.16</v>
-      </c>
-      <c r="H22" s="51">
-        <f>G22</f>
-        <v>10980.16</v>
-      </c>
+        <v>8646.16</v>
+      </c>
+      <c r="H22" s="51"/>
       <c r="I22" s="52"/>
       <c r="J22" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8646.16</v>
       </c>
       <c r="K22" s="53">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>259.38479999999998</v>
       </c>
       <c r="L22" s="54">
         <f t="shared" si="4"/>
-        <v>67.099999999999994</v>
+        <v>128.1</v>
       </c>
       <c r="M22" s="54">
         <f t="shared" si="5"/>
-        <v>8578.805210999999</v>
+        <v>10370</v>
       </c>
       <c r="N22" s="55">
         <v>0</v>
       </c>
       <c r="O22" s="56">
         <f t="shared" si="6"/>
-        <v>8646.16</v>
+        <v>19404.16</v>
       </c>
       <c r="P22" s="57">
         <f t="shared" si="0"/>
-        <v>8905.16</v>
+        <v>19986.16</v>
       </c>
       <c r="Q22" s="35">
         <f t="shared" si="7"/>
@@ -4273,11 +4288,11 @@
       </c>
       <c r="G24" s="40">
         <f>SUM(G7:G23)</f>
-        <v>5065159.3599999994</v>
+        <v>5041116.3599999994</v>
       </c>
       <c r="H24" s="44">
         <f>SUM(H7:H23)</f>
-        <v>2022091.92</v>
+        <v>1320859.99</v>
       </c>
       <c r="I24" s="44">
         <f>SUM(I7:I23)</f>
@@ -4287,23 +4302,23 @@
       <c r="K24" s="44"/>
       <c r="L24" s="44">
         <f>SUM(L7:L23)</f>
-        <v>11000.000000000002</v>
+        <v>21000</v>
       </c>
       <c r="M24" s="44">
         <f>SUM(M7:M23)</f>
-        <v>1406361.5100000002</v>
+        <v>1700000</v>
       </c>
       <c r="N24" s="44">
         <f>SUM(N7:N23)</f>
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="O24" s="67">
         <f>SUM(O7:O22)</f>
-        <v>5031739.3599999994</v>
+        <v>5553142.3599999994</v>
       </c>
       <c r="P24" s="67">
         <f>SUM(P7:P22)</f>
-        <v>5182689.3599999994</v>
+        <v>5719734.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
@@ -4312,93 +4327,98 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="9" customHeight="1">
-      <c r="D27" s="182" t="s">
+      <c r="D27" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="182"/>
-      <c r="F27" s="182"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="182"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="182"/>
-      <c r="N27" s="182"/>
-      <c r="O27" s="182"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="175"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="175"/>
+      <c r="M27" s="175"/>
+      <c r="N27" s="175"/>
+      <c r="O27" s="175"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="182"/>
-      <c r="E28" s="182"/>
-      <c r="F28" s="182"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="182"/>
-      <c r="I28" s="182"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="182"/>
-      <c r="N28" s="182"/>
-      <c r="O28" s="182"/>
+      <c r="D28" s="175"/>
+      <c r="E28" s="175"/>
+      <c r="F28" s="175"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="175"/>
+      <c r="I28" s="175"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="175"/>
+      <c r="L28" s="175"/>
+      <c r="M28" s="175"/>
+      <c r="N28" s="175"/>
+      <c r="O28" s="175"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="182"/>
-      <c r="E29" s="182"/>
-      <c r="F29" s="182"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="182"/>
-      <c r="I29" s="182"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="182"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="182"/>
-      <c r="N29" s="182"/>
-      <c r="O29" s="182"/>
+      <c r="D29" s="175"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="175"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="175"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="175"/>
+      <c r="N29" s="175"/>
+      <c r="O29" s="175"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="182"/>
-      <c r="E30" s="182"/>
-      <c r="F30" s="182"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="182"/>
-      <c r="I30" s="182"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="182"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="175"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="175"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="175"/>
+      <c r="L30" s="175"/>
+      <c r="M30" s="175"/>
+      <c r="N30" s="175"/>
+      <c r="O30" s="175"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="182"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="182"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="182"/>
-      <c r="I31" s="182"/>
-      <c r="J31" s="182"/>
-      <c r="K31" s="182"/>
-      <c r="L31" s="182"/>
-      <c r="M31" s="182"/>
-      <c r="N31" s="182"/>
-      <c r="O31" s="182"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="175"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="175"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="175"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="182"/>
-      <c r="E32" s="182"/>
-      <c r="F32" s="182"/>
-      <c r="G32" s="182"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="182"/>
-      <c r="J32" s="182"/>
-      <c r="K32" s="182"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="182"/>
-      <c r="O32" s="182"/>
+      <c r="D32" s="175"/>
+      <c r="E32" s="175"/>
+      <c r="F32" s="175"/>
+      <c r="G32" s="175"/>
+      <c r="H32" s="175"/>
+      <c r="I32" s="175"/>
+      <c r="J32" s="175"/>
+      <c r="K32" s="175"/>
+      <c r="L32" s="175"/>
+      <c r="M32" s="175"/>
+      <c r="N32" s="175"/>
+      <c r="O32" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4412,11 +4432,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>

--- a/2026/BELTRAN 34/Febrero/Febrero BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Febrero/Febrero BELTRAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA8B32C-5B90-40CE-9C27-0712643C110B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E9C5FE-ED19-4B13-9DEA-319784E63DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1711,6 +1711,18 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1726,9 +1738,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1758,15 +1767,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2402,8 +2402,8 @@
       </c>
       <c r="B32" s="147"/>
       <c r="C32" s="111">
-        <f>147400*2</f>
-        <v>294800</v>
+        <f>147400</f>
+        <v>147400</v>
       </c>
       <c r="D32" s="109" t="s">
         <v>124</v>
@@ -2421,7 +2421,7 @@
       <c r="C33" s="27"/>
       <c r="D33" s="72">
         <f>SUM(C32:C32)</f>
-        <v>294800</v>
+        <v>147400</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1">
@@ -2707,7 +2707,7 @@
       <c r="C61" s="87"/>
       <c r="D61" s="88">
         <f>(SUM(D25:D59))</f>
-        <v>1940906.32</v>
+        <v>1793506.32</v>
       </c>
       <c r="E61" s="35"/>
       <c r="F61" s="35"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B75" s="69">
         <f>D61</f>
-        <v>1940906.32</v>
+        <v>1793506.32</v>
       </c>
       <c r="C75" s="35"/>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="B76" s="69">
         <f>D61-D59</f>
-        <v>1940906.32</v>
+        <v>1793506.32</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" thickBot="1">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B88" s="105">
         <f>-B76</f>
-        <v>-1940906.32</v>
+        <v>-1793506.32</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B90" s="129">
         <f>SUM(B83:B89)</f>
-        <v>43276.979999999749</v>
+        <v>190676.97999999975</v>
       </c>
       <c r="C90" s="157"/>
     </row>
@@ -2988,22 +2988,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="130"/>
-      <c r="B1" s="171" t="str">
+      <c r="B1" s="175" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
       <c r="L1" s="131"/>
       <c r="M1" s="131"/>
       <c r="N1" s="131"/>
@@ -3012,16 +3012,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="133"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
       <c r="L2" s="134"/>
       <c r="M2" s="134" t="s">
         <v>4</v>
@@ -3038,16 +3038,16 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="136"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="B3" s="177"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
+      <c r="K3" s="177"/>
       <c r="L3" s="137"/>
       <c r="M3" s="137" t="s">
         <v>56</v>
@@ -3060,96 +3060,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="184" t="s">
+      <c r="B4" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
-      <c r="N4" s="185"/>
-      <c r="O4" s="185"/>
-      <c r="P4" s="186"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="188"/>
+      <c r="H4" s="188"/>
+      <c r="I4" s="188"/>
+      <c r="J4" s="188"/>
+      <c r="K4" s="188"/>
+      <c r="L4" s="188"/>
+      <c r="M4" s="188"/>
+      <c r="N4" s="188"/>
+      <c r="O4" s="188"/>
+      <c r="P4" s="189"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="187" t="s">
+      <c r="A5" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="189" t="s">
+      <c r="B5" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="176" t="s">
+      <c r="C5" s="174" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="176" t="s">
+      <c r="D5" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="176" t="s">
+      <c r="E5" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="176" t="s">
+      <c r="F5" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="176" t="s">
+      <c r="G5" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="176" t="s">
+      <c r="H5" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="176" t="s">
+      <c r="I5" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="180" t="s">
+      <c r="J5" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="178" t="s">
+      <c r="K5" s="181" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="178" t="s">
+      <c r="L5" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="178" t="s">
+      <c r="M5" s="181" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="182" t="s">
+      <c r="N5" s="185" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="174" t="s">
+      <c r="P5" s="178" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="35"/>
       <c r="T5" s="33"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="188"/>
-      <c r="B6" s="189"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="179"/>
-      <c r="N6" s="183"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="180"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="180"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="181"/>
+      <c r="M6" s="182"/>
+      <c r="N6" s="186"/>
       <c r="O6" s="43" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P6" s="174"/>
+      <c r="P6" s="178"/>
       <c r="S6" s="33">
         <v>65160</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>151374.07999999999</v>
       </c>
       <c r="H14" s="51">
-        <f t="shared" ref="H13:H18" si="8">G14</f>
+        <f t="shared" ref="H14:H18" si="8">G14</f>
         <v>151374.07999999999</v>
       </c>
       <c r="I14" s="52"/>
@@ -4327,98 +4327,93 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="9" customHeight="1">
-      <c r="D27" s="175" t="s">
+      <c r="D27" s="179" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="175"/>
-      <c r="F27" s="175"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="175"/>
-      <c r="I27" s="175"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="175"/>
-      <c r="L27" s="175"/>
-      <c r="M27" s="175"/>
-      <c r="N27" s="175"/>
-      <c r="O27" s="175"/>
+      <c r="E27" s="179"/>
+      <c r="F27" s="179"/>
+      <c r="G27" s="179"/>
+      <c r="H27" s="179"/>
+      <c r="I27" s="179"/>
+      <c r="J27" s="179"/>
+      <c r="K27" s="179"/>
+      <c r="L27" s="179"/>
+      <c r="M27" s="179"/>
+      <c r="N27" s="179"/>
+      <c r="O27" s="179"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="175"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="175"/>
-      <c r="I28" s="175"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="175"/>
-      <c r="L28" s="175"/>
-      <c r="M28" s="175"/>
-      <c r="N28" s="175"/>
-      <c r="O28" s="175"/>
+      <c r="D28" s="179"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="179"/>
+      <c r="I28" s="179"/>
+      <c r="J28" s="179"/>
+      <c r="K28" s="179"/>
+      <c r="L28" s="179"/>
+      <c r="M28" s="179"/>
+      <c r="N28" s="179"/>
+      <c r="O28" s="179"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="175"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="175"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="175"/>
-      <c r="I29" s="175"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="175"/>
-      <c r="L29" s="175"/>
-      <c r="M29" s="175"/>
-      <c r="N29" s="175"/>
-      <c r="O29" s="175"/>
+      <c r="D29" s="179"/>
+      <c r="E29" s="179"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="179"/>
+      <c r="H29" s="179"/>
+      <c r="I29" s="179"/>
+      <c r="J29" s="179"/>
+      <c r="K29" s="179"/>
+      <c r="L29" s="179"/>
+      <c r="M29" s="179"/>
+      <c r="N29" s="179"/>
+      <c r="O29" s="179"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="175"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="175"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="175"/>
-      <c r="I30" s="175"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="175"/>
-      <c r="L30" s="175"/>
-      <c r="M30" s="175"/>
-      <c r="N30" s="175"/>
-      <c r="O30" s="175"/>
+      <c r="D30" s="179"/>
+      <c r="E30" s="179"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="179"/>
+      <c r="I30" s="179"/>
+      <c r="J30" s="179"/>
+      <c r="K30" s="179"/>
+      <c r="L30" s="179"/>
+      <c r="M30" s="179"/>
+      <c r="N30" s="179"/>
+      <c r="O30" s="179"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="175"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
-      <c r="L31" s="175"/>
-      <c r="M31" s="175"/>
-      <c r="N31" s="175"/>
-      <c r="O31" s="175"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="179"/>
+      <c r="I31" s="179"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="179"/>
+      <c r="N31" s="179"/>
+      <c r="O31" s="179"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="175"/>
-      <c r="E32" s="175"/>
-      <c r="F32" s="175"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="175"/>
-      <c r="I32" s="175"/>
-      <c r="J32" s="175"/>
-      <c r="K32" s="175"/>
-      <c r="L32" s="175"/>
-      <c r="M32" s="175"/>
-      <c r="N32" s="175"/>
-      <c r="O32" s="175"/>
+      <c r="D32" s="179"/>
+      <c r="E32" s="179"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="179"/>
+      <c r="I32" s="179"/>
+      <c r="J32" s="179"/>
+      <c r="K32" s="179"/>
+      <c r="L32" s="179"/>
+      <c r="M32" s="179"/>
+      <c r="N32" s="179"/>
+      <c r="O32" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4432,6 +4427,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
